--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 BLACK BEAR DRAW.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 BLACK BEAR DRAW.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hunt Table'!$A$1:$O$107</definedName>
@@ -1689,7 +1689,11 @@
       <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="5" t="inlineStr"/>
       <c r="M21" s="5" t="inlineStr"/>
-      <c r="N21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
       <c r="O21" s="5" t="inlineStr"/>
     </row>
     <row r="22" ht="28" customHeight="1">
@@ -1803,7 +1807,11 @@
       <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr"/>
-      <c r="N23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O23" s="5" t="inlineStr"/>
     </row>
     <row r="24" ht="28" customHeight="1">
@@ -2202,7 +2210,11 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="3" t="inlineStr"/>
       <c r="M30" s="3" t="inlineStr"/>
-      <c r="N30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
       <c r="O30" s="3" t="inlineStr"/>
     </row>
     <row r="31" ht="28" customHeight="1">
@@ -2259,7 +2271,11 @@
       <c r="K31" s="4" t="inlineStr"/>
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
-      <c r="N31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="O31" s="5" t="inlineStr"/>
     </row>
     <row r="32" ht="28" customHeight="1">
@@ -3000,7 +3016,11 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="inlineStr"/>
       <c r="M44" s="3" t="inlineStr"/>
-      <c r="N44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O44" s="3" t="inlineStr"/>
     </row>
     <row r="45" ht="28" customHeight="1">
@@ -4710,7 +4730,11 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="3" t="inlineStr"/>
       <c r="M74" s="3" t="inlineStr"/>
-      <c r="N74" s="3" t="inlineStr"/>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
       <c r="O74" s="3" t="inlineStr"/>
     </row>
     <row r="75" ht="28" customHeight="1">
@@ -4881,7 +4905,11 @@
       <c r="K77" s="4" t="inlineStr"/>
       <c r="L77" s="5" t="inlineStr"/>
       <c r="M77" s="5" t="inlineStr"/>
-      <c r="N77" s="5" t="inlineStr"/>
+      <c r="N77" s="5" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
       <c r="O77" s="5" t="inlineStr"/>
     </row>
     <row r="78" ht="28" customHeight="1">
@@ -4938,7 +4966,11 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="3" t="inlineStr"/>
       <c r="M78" s="3" t="inlineStr"/>
-      <c r="N78" s="3" t="inlineStr"/>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
       <c r="O78" s="3" t="inlineStr"/>
     </row>
     <row r="79" ht="28" customHeight="1">
@@ -4995,7 +5027,11 @@
       <c r="K79" s="4" t="inlineStr"/>
       <c r="L79" s="5" t="inlineStr"/>
       <c r="M79" s="5" t="inlineStr"/>
-      <c r="N79" s="5" t="inlineStr"/>
+      <c r="N79" s="5" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="O79" s="5" t="inlineStr"/>
     </row>
     <row r="80" ht="28" customHeight="1">
@@ -5052,7 +5088,11 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="3" t="inlineStr"/>
       <c r="M80" s="3" t="inlineStr"/>
-      <c r="N80" s="3" t="inlineStr"/>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
       <c r="O80" s="3" t="inlineStr"/>
     </row>
     <row r="81" ht="28" customHeight="1">
@@ -5337,7 +5377,11 @@
       <c r="K85" s="4" t="inlineStr"/>
       <c r="L85" s="5" t="inlineStr"/>
       <c r="M85" s="5" t="inlineStr"/>
-      <c r="N85" s="5" t="inlineStr"/>
+      <c r="N85" s="5" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
       <c r="O85" s="5" t="inlineStr"/>
     </row>
     <row r="86" ht="28" customHeight="1">
@@ -5781,7 +5825,11 @@
       <c r="K93" s="4" t="inlineStr"/>
       <c r="L93" s="5" t="inlineStr"/>
       <c r="M93" s="5" t="inlineStr"/>
-      <c r="N93" s="5" t="inlineStr"/>
+      <c r="N93" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="O93" s="5" t="inlineStr"/>
     </row>
     <row r="94" ht="28" customHeight="1">
@@ -6237,7 +6285,11 @@
       <c r="K101" s="4" t="inlineStr"/>
       <c r="L101" s="5" t="inlineStr"/>
       <c r="M101" s="5" t="inlineStr"/>
-      <c r="N101" s="5" t="inlineStr"/>
+      <c r="N101" s="5" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="O101" s="5" t="inlineStr"/>
     </row>
     <row r="102" ht="28" customHeight="1">
@@ -6351,7 +6403,11 @@
       <c r="K103" s="4" t="inlineStr"/>
       <c r="L103" s="5" t="inlineStr"/>
       <c r="M103" s="5" t="inlineStr"/>
-      <c r="N103" s="5" t="inlineStr"/>
+      <c r="N103" s="5" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
       <c r="O103" s="5" t="inlineStr"/>
     </row>
     <row r="104" ht="28" customHeight="1">
@@ -6408,7 +6464,11 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="3" t="inlineStr"/>
       <c r="M104" s="3" t="inlineStr"/>
-      <c r="N104" s="3" t="inlineStr"/>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O104" s="3" t="inlineStr"/>
     </row>
     <row r="105" ht="28" customHeight="1">
@@ -6453,7 +6513,11 @@
       <c r="K105" s="4" t="inlineStr"/>
       <c r="L105" s="5" t="inlineStr"/>
       <c r="M105" s="5" t="inlineStr"/>
-      <c r="N105" s="5" t="inlineStr"/>
+      <c r="N105" s="5" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
       <c r="O105" s="5" t="inlineStr"/>
     </row>
     <row r="106" ht="28" customHeight="1">
